--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonir\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonir\Downloads\CSM-Noatum-deviation-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB92C79D-5401-472B-AAB5-A5AE7F56528C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6034FA48-A85D-4718-9212-DEDE4A6339DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{70D0A116-D27A-458B-9A0C-5A6A446D71F4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{70D0A116-D27A-458B-9A0C-5A6A446D71F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1(25 May-31 May)" sheetId="4" r:id="rId1"/>
     <sheet name="Week 2(01 Jun - 07 Jun)" sheetId="3" r:id="rId2"/>
     <sheet name="Week 3(08 Jun - 15 Jun)" sheetId="2" r:id="rId3"/>
     <sheet name="Week 4(16 Jun - 22 Jun)" sheetId="1" r:id="rId4"/>
-    <sheet name="Mail info" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 5(23 Jun - 29 Jun)" sheetId="6" r:id="rId5"/>
+    <sheet name="Mail info" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="315">
   <si>
     <t>Ship Name</t>
   </si>
@@ -893,6 +894,124 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Avg. Speed</t>
+  </si>
+  <si>
+    <t>003B</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 204.11 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 231.93 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 213.12 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 215.64 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 202.10 g/kwh)</t>
+  </si>
+  <si>
+    <t>625N</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 217.98 g/kwh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JNH-FES2604E </t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 35.25 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-21 23:15:00, Curr Start: 2026-06-20 12:00:00) | Report Info: 20-Jun-26 12:00</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 18.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-21 12:00:00, Curr Start: 2026-06-22 06:00:00) | Report Info: 22-Jun-26 06:00</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 13.88 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-22 14:25:00, Curr Start: 2026-06-23 04:18:00) | Report Info: 23-Jun-26 04:18</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 203.22 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 207.61 g/kwh)</t>
+  </si>
+  <si>
+    <t>Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.; Rule 7 (Reporting Gap): There is a 14.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-20 22:00:00, Curr Start: 2026-06-21 12:00:00) | Report Info: 21-Jun-26 12:00</t>
+  </si>
+  <si>
+    <t>31LA</t>
+  </si>
+  <si>
+    <t>Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 3.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 25.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-26 19:48:00, Curr Start: 2026-06-25 18:48:00) | Report Info: 25-Jun-26 18:48</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 7.80 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-26 12:00:00, Curr Start: 2026-06-26 19:48:00) | Report Info: 26-Jun-26 19:48</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 4</t>
+  </si>
+  <si>
+    <t>004B26</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 107.73 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>004B</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 107.73 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 111.29 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 97.80 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.09) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>Exhaust temp deviation &gt; ±50 from avg at Unit 2; Exhaust temp deviation &gt; ±50 from avg at Unit 3; Exhaust temp deviation &gt; ±50 from avg at Unit 8; SFOC out of 170-240 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 94.51 g/kwh); Validation – 2 Aux Engines operating at sea with ME Load greater than 40% (Ratio: 2.00) and no sub consumers reported.
+Kindly confirm that if auxiliary engines are operated for activities including tank cleaning, cargo transfer, ballast operations, or similar tasks, the corresponding estimated fuel consumption (in metric tons) should be entered under the relevant option in the Sub Fuel Consumers section. If a suitable option is not listed, please use the “Others” category within the Daily Report.</t>
+  </si>
+  <si>
+    <t>UARGFS2611</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 208.65 g/kwh)</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 221.50 g/kwh)</t>
+  </si>
+  <si>
+    <t>uargfs2611</t>
+  </si>
+  <si>
+    <t>SFOC out of 150-200 g/kwh at sea with ME Rhrs &gt; 12 (Calculated SFOC: 213.41 g/kwh)</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 48.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-25 00:00:00, Curr Start: 2026-06-23 00:00:00) | Report Info: 23-Jun-26 00:00</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 24.00 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-24 00:00:00, Curr Start: 2026-06-25 00:00:00) | Report Info: 25-Jun-26 00:00</t>
+  </si>
+  <si>
+    <t>UBCGFS2609</t>
+  </si>
+  <si>
+    <t>Rule 7 (Reporting Gap): There is a 14.20 hour gap between the end date and time of previous report and start date and time in current report (Prev End: 2026-06-23 12:00:00, Curr Start: 2026-06-24 02:12:00) | Report Info: 24-Jun-26 02:12</t>
   </si>
 </sst>
 </file>
@@ -936,7 +1055,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -955,6 +1074,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15162,6 +15284,3322 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CF76CC-CEDA-4189-AD0C-0BE631B4F1C6}">
+  <dimension ref="A1:AJ42"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>278</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2">
+        <v>153</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>153</v>
+      </c>
+      <c r="I2">
+        <v>3780</v>
+      </c>
+      <c r="J2">
+        <v>97.7</v>
+      </c>
+      <c r="K2">
+        <v>39.9</v>
+      </c>
+      <c r="L2">
+        <v>12.3</v>
+      </c>
+      <c r="M2">
+        <v>12.3</v>
+      </c>
+      <c r="N2">
+        <v>9.49</v>
+      </c>
+      <c r="O2">
+        <v>353</v>
+      </c>
+      <c r="P2">
+        <v>354</v>
+      </c>
+      <c r="Q2">
+        <v>354</v>
+      </c>
+      <c r="R2">
+        <v>356</v>
+      </c>
+      <c r="S2">
+        <v>355</v>
+      </c>
+      <c r="T2">
+        <v>356</v>
+      </c>
+      <c r="AE2">
+        <v>51</v>
+      </c>
+      <c r="AF2">
+        <v>204.11235859999999</v>
+      </c>
+      <c r="AG2">
+        <v>12.3</v>
+      </c>
+      <c r="AH2">
+        <v>12.44</v>
+      </c>
+      <c r="AI2">
+        <v>0.98722415799999996</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D3">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>314</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>314</v>
+      </c>
+      <c r="I3">
+        <v>4654.96</v>
+      </c>
+      <c r="J3">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="K3">
+        <v>21.49</v>
+      </c>
+      <c r="L3">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>24</v>
+      </c>
+      <c r="N3">
+        <v>25.9</v>
+      </c>
+      <c r="O3">
+        <v>328</v>
+      </c>
+      <c r="P3">
+        <v>294</v>
+      </c>
+      <c r="Q3">
+        <v>309</v>
+      </c>
+      <c r="R3">
+        <v>284</v>
+      </c>
+      <c r="S3">
+        <v>288</v>
+      </c>
+      <c r="T3">
+        <v>304</v>
+      </c>
+      <c r="AE3">
+        <v>112</v>
+      </c>
+      <c r="AF3">
+        <v>231.83156600000001</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>13.08</v>
+      </c>
+      <c r="AI3">
+        <v>0.90226339200000005</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4">
+        <v>342</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>342</v>
+      </c>
+      <c r="I4">
+        <v>4658.3999999999996</v>
+      </c>
+      <c r="J4">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="K4">
+        <v>21.51</v>
+      </c>
+      <c r="L4">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>27.01</v>
+      </c>
+      <c r="O4">
+        <v>329</v>
+      </c>
+      <c r="P4">
+        <v>296</v>
+      </c>
+      <c r="Q4">
+        <v>313</v>
+      </c>
+      <c r="R4">
+        <v>291</v>
+      </c>
+      <c r="S4">
+        <v>301</v>
+      </c>
+      <c r="T4">
+        <v>305</v>
+      </c>
+      <c r="AE4">
+        <v>122</v>
+      </c>
+      <c r="AF4">
+        <v>231.92512450000001</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>13.68</v>
+      </c>
+      <c r="AI4">
+        <v>0.94281298300000005</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5">
+        <v>303</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>303</v>
+      </c>
+      <c r="I5">
+        <v>4852.6899999999996</v>
+      </c>
+      <c r="J5">
+        <v>64.2</v>
+      </c>
+      <c r="K5">
+        <v>22.4</v>
+      </c>
+      <c r="L5">
+        <v>23.4</v>
+      </c>
+      <c r="M5">
+        <v>24</v>
+      </c>
+      <c r="N5">
+        <v>24.2</v>
+      </c>
+      <c r="O5">
+        <v>314</v>
+      </c>
+      <c r="P5">
+        <v>296</v>
+      </c>
+      <c r="Q5">
+        <v>285</v>
+      </c>
+      <c r="R5">
+        <v>281</v>
+      </c>
+      <c r="S5">
+        <v>286</v>
+      </c>
+      <c r="T5">
+        <v>297</v>
+      </c>
+      <c r="AE5">
+        <v>115</v>
+      </c>
+      <c r="AF5">
+        <v>213.1164435</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>12.63</v>
+      </c>
+      <c r="AI5">
+        <v>0.91146908699999996</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6">
+        <v>215</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>215</v>
+      </c>
+      <c r="I6">
+        <v>4753.3900000000003</v>
+      </c>
+      <c r="J6">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="K6">
+        <v>21.95</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
+        <v>18</v>
+      </c>
+      <c r="N6">
+        <v>18.45</v>
+      </c>
+      <c r="O6">
+        <v>320</v>
+      </c>
+      <c r="P6">
+        <v>293</v>
+      </c>
+      <c r="Q6">
+        <v>302</v>
+      </c>
+      <c r="R6">
+        <v>295</v>
+      </c>
+      <c r="S6">
+        <v>293</v>
+      </c>
+      <c r="T6">
+        <v>283</v>
+      </c>
+      <c r="AE6">
+        <v>84</v>
+      </c>
+      <c r="AF6">
+        <v>215.63557800000001</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>11.94</v>
+      </c>
+      <c r="AI6">
+        <v>0.88357992900000004</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>280</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>280</v>
+      </c>
+      <c r="I7">
+        <v>5200</v>
+      </c>
+      <c r="J7">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="K7">
+        <v>24.01</v>
+      </c>
+      <c r="L7">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>22</v>
+      </c>
+      <c r="N7">
+        <v>23.12</v>
+      </c>
+      <c r="O7">
+        <v>324</v>
+      </c>
+      <c r="P7">
+        <v>301</v>
+      </c>
+      <c r="Q7">
+        <v>303</v>
+      </c>
+      <c r="R7">
+        <v>294</v>
+      </c>
+      <c r="S7">
+        <v>293</v>
+      </c>
+      <c r="T7">
+        <v>288</v>
+      </c>
+      <c r="AE7">
+        <v>102</v>
+      </c>
+      <c r="AF7">
+        <v>202.0979021</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>12.73</v>
+      </c>
+      <c r="AI7">
+        <v>0.80244755199999995</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>285</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>286</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>277</v>
+      </c>
+      <c r="I8">
+        <v>8315</v>
+      </c>
+      <c r="J8">
+        <v>60</v>
+      </c>
+      <c r="K8">
+        <v>23</v>
+      </c>
+      <c r="L8">
+        <v>24</v>
+      </c>
+      <c r="M8">
+        <v>24</v>
+      </c>
+      <c r="N8">
+        <v>43.5</v>
+      </c>
+      <c r="O8">
+        <v>289</v>
+      </c>
+      <c r="P8">
+        <v>320</v>
+      </c>
+      <c r="Q8">
+        <v>310</v>
+      </c>
+      <c r="R8">
+        <v>299</v>
+      </c>
+      <c r="S8">
+        <v>330</v>
+      </c>
+      <c r="T8">
+        <v>310</v>
+      </c>
+      <c r="U8">
+        <v>320</v>
+      </c>
+      <c r="V8">
+        <v>305</v>
+      </c>
+      <c r="AE8">
+        <v>245</v>
+      </c>
+      <c r="AF8">
+        <v>217.979555</v>
+      </c>
+      <c r="AG8">
+        <v>24</v>
+      </c>
+      <c r="AH8">
+        <v>11.92</v>
+      </c>
+      <c r="AI8">
+        <v>1.104930848</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>287</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>24</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>4600</v>
+      </c>
+      <c r="J10">
+        <v>500</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>8.42</v>
+      </c>
+      <c r="N10">
+        <v>2.1</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>152.173913</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>7</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>0.17916666666666667</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>2800</v>
+      </c>
+      <c r="J11">
+        <v>500</v>
+      </c>
+      <c r="K11">
+        <v>38</v>
+      </c>
+      <c r="L11">
+        <v>3.5</v>
+      </c>
+      <c r="M11">
+        <v>3.37</v>
+      </c>
+      <c r="N11">
+        <v>2.5</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>255.1020408</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>6</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12">
+        <v>331</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>289</v>
+      </c>
+      <c r="I12">
+        <v>3137</v>
+      </c>
+      <c r="J12">
+        <v>98</v>
+      </c>
+      <c r="K12">
+        <v>50</v>
+      </c>
+      <c r="L12">
+        <v>24</v>
+      </c>
+      <c r="M12">
+        <v>24</v>
+      </c>
+      <c r="N12">
+        <v>15.3</v>
+      </c>
+      <c r="O12">
+        <v>361</v>
+      </c>
+      <c r="P12">
+        <v>352</v>
+      </c>
+      <c r="Q12">
+        <v>327</v>
+      </c>
+      <c r="R12">
+        <v>354</v>
+      </c>
+      <c r="S12">
+        <v>359</v>
+      </c>
+      <c r="AE12">
+        <v>104</v>
+      </c>
+      <c r="AF12">
+        <v>203.2196366</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>13.79</v>
+      </c>
+      <c r="AI12">
+        <v>1.243226012</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13">
+        <v>269</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>271</v>
+      </c>
+      <c r="I13">
+        <v>3171</v>
+      </c>
+      <c r="J13">
+        <v>97</v>
+      </c>
+      <c r="K13">
+        <v>48</v>
+      </c>
+      <c r="L13">
+        <v>24</v>
+      </c>
+      <c r="M13">
+        <v>24</v>
+      </c>
+      <c r="N13">
+        <v>15.8</v>
+      </c>
+      <c r="O13">
+        <v>345</v>
+      </c>
+      <c r="P13">
+        <v>342</v>
+      </c>
+      <c r="Q13">
+        <v>319</v>
+      </c>
+      <c r="R13">
+        <v>330</v>
+      </c>
+      <c r="S13">
+        <v>345</v>
+      </c>
+      <c r="AE13">
+        <v>104</v>
+      </c>
+      <c r="AF13">
+        <v>207.61063809999999</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>11.21</v>
+      </c>
+      <c r="AI13">
+        <v>1.229895932</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46193</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>48</v>
+      </c>
+      <c r="I14">
+        <v>3090</v>
+      </c>
+      <c r="J14">
+        <v>54.24</v>
+      </c>
+      <c r="K14">
+        <v>28.8</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>0.89</v>
+      </c>
+      <c r="AE14">
+        <v>11</v>
+      </c>
+      <c r="AF14">
+        <v>144.012945</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+      <c r="AH14">
+        <v>8</v>
+      </c>
+      <c r="AI14">
+        <v>1.601941748</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>264</v>
+      </c>
+      <c r="I15">
+        <v>4954</v>
+      </c>
+      <c r="J15">
+        <v>72.69</v>
+      </c>
+      <c r="K15">
+        <v>46.1</v>
+      </c>
+      <c r="L15">
+        <v>24</v>
+      </c>
+      <c r="M15">
+        <v>24</v>
+      </c>
+      <c r="N15">
+        <v>21.4</v>
+      </c>
+      <c r="O15">
+        <v>365</v>
+      </c>
+      <c r="P15">
+        <v>358</v>
+      </c>
+      <c r="Q15">
+        <v>340</v>
+      </c>
+      <c r="R15">
+        <v>332</v>
+      </c>
+      <c r="S15">
+        <v>380</v>
+      </c>
+      <c r="T15">
+        <v>330</v>
+      </c>
+      <c r="AE15">
+        <v>130</v>
+      </c>
+      <c r="AF15">
+        <v>179.98923429999999</v>
+      </c>
+      <c r="AG15">
+        <v>24</v>
+      </c>
+      <c r="AH15">
+        <v>10.7</v>
+      </c>
+      <c r="AI15">
+        <v>0.98405328999999997</v>
+      </c>
+      <c r="AJ15" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16">
+        <v>260</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>256</v>
+      </c>
+      <c r="I16">
+        <v>4958</v>
+      </c>
+      <c r="J16">
+        <v>71.2</v>
+      </c>
+      <c r="K16">
+        <v>46.2</v>
+      </c>
+      <c r="L16">
+        <v>24</v>
+      </c>
+      <c r="M16">
+        <v>24</v>
+      </c>
+      <c r="N16">
+        <v>21.42</v>
+      </c>
+      <c r="O16">
+        <v>362</v>
+      </c>
+      <c r="P16">
+        <v>368</v>
+      </c>
+      <c r="Q16">
+        <v>338</v>
+      </c>
+      <c r="R16">
+        <v>329</v>
+      </c>
+      <c r="S16">
+        <v>376</v>
+      </c>
+      <c r="T16">
+        <v>333</v>
+      </c>
+      <c r="AE16">
+        <v>130</v>
+      </c>
+      <c r="AF16">
+        <v>180.01210169999999</v>
+      </c>
+      <c r="AG16">
+        <v>24</v>
+      </c>
+      <c r="AH16">
+        <v>10.75</v>
+      </c>
+      <c r="AI16">
+        <v>0.98325937900000004</v>
+      </c>
+      <c r="AJ16" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17">
+        <v>253</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>256</v>
+      </c>
+      <c r="I17">
+        <v>4641</v>
+      </c>
+      <c r="J17">
+        <v>69.94</v>
+      </c>
+      <c r="K17">
+        <v>43.2</v>
+      </c>
+      <c r="L17">
+        <v>24</v>
+      </c>
+      <c r="M17">
+        <v>24</v>
+      </c>
+      <c r="N17">
+        <v>20.05</v>
+      </c>
+      <c r="O17">
+        <v>342</v>
+      </c>
+      <c r="P17">
+        <v>345</v>
+      </c>
+      <c r="Q17">
+        <v>320</v>
+      </c>
+      <c r="R17">
+        <v>315</v>
+      </c>
+      <c r="S17">
+        <v>349</v>
+      </c>
+      <c r="T17">
+        <v>305</v>
+      </c>
+      <c r="AE17">
+        <v>122</v>
+      </c>
+      <c r="AF17">
+        <v>180.0079006</v>
+      </c>
+      <c r="AG17">
+        <v>24</v>
+      </c>
+      <c r="AH17">
+        <v>10.54</v>
+      </c>
+      <c r="AI17">
+        <v>0.98577892700000003</v>
+      </c>
+      <c r="AJ17" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>294</v>
+      </c>
+      <c r="E18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18">
+        <v>250</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>256</v>
+      </c>
+      <c r="I18">
+        <v>4907</v>
+      </c>
+      <c r="J18">
+        <v>71.34</v>
+      </c>
+      <c r="K18">
+        <v>45.7</v>
+      </c>
+      <c r="L18">
+        <v>24</v>
+      </c>
+      <c r="M18">
+        <v>24</v>
+      </c>
+      <c r="N18">
+        <v>21.2</v>
+      </c>
+      <c r="O18">
+        <v>362</v>
+      </c>
+      <c r="P18">
+        <v>365</v>
+      </c>
+      <c r="Q18">
+        <v>332</v>
+      </c>
+      <c r="R18">
+        <v>334</v>
+      </c>
+      <c r="S18">
+        <v>377</v>
+      </c>
+      <c r="T18">
+        <v>327</v>
+      </c>
+      <c r="AE18">
+        <v>128</v>
+      </c>
+      <c r="AF18">
+        <v>180.01494460000001</v>
+      </c>
+      <c r="AG18">
+        <v>24</v>
+      </c>
+      <c r="AH18">
+        <v>10.41</v>
+      </c>
+      <c r="AI18">
+        <v>0.97819441600000001</v>
+      </c>
+      <c r="AJ18" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19">
+        <v>258</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>252</v>
+      </c>
+      <c r="I19">
+        <v>4907</v>
+      </c>
+      <c r="J19">
+        <v>71.19</v>
+      </c>
+      <c r="K19">
+        <v>45.7</v>
+      </c>
+      <c r="L19">
+        <v>24</v>
+      </c>
+      <c r="M19">
+        <v>24</v>
+      </c>
+      <c r="N19">
+        <v>21.2</v>
+      </c>
+      <c r="O19">
+        <v>365</v>
+      </c>
+      <c r="P19">
+        <v>360</v>
+      </c>
+      <c r="Q19">
+        <v>339</v>
+      </c>
+      <c r="R19">
+        <v>329</v>
+      </c>
+      <c r="S19">
+        <v>379</v>
+      </c>
+      <c r="T19">
+        <v>319</v>
+      </c>
+      <c r="AE19">
+        <v>128</v>
+      </c>
+      <c r="AF19">
+        <v>180.01494460000001</v>
+      </c>
+      <c r="AG19">
+        <v>24</v>
+      </c>
+      <c r="AH19">
+        <v>10.75</v>
+      </c>
+      <c r="AI19">
+        <v>0.97819441600000001</v>
+      </c>
+      <c r="AJ19" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20">
+        <v>269</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>272</v>
+      </c>
+      <c r="I20">
+        <v>4968</v>
+      </c>
+      <c r="J20">
+        <v>72</v>
+      </c>
+      <c r="K20">
+        <v>46.3</v>
+      </c>
+      <c r="L20">
+        <v>24</v>
+      </c>
+      <c r="M20">
+        <v>24</v>
+      </c>
+      <c r="N20">
+        <v>21.46</v>
+      </c>
+      <c r="O20">
+        <v>354</v>
+      </c>
+      <c r="P20">
+        <v>351</v>
+      </c>
+      <c r="Q20">
+        <v>333</v>
+      </c>
+      <c r="R20">
+        <v>326</v>
+      </c>
+      <c r="S20">
+        <v>369</v>
+      </c>
+      <c r="T20">
+        <v>320</v>
+      </c>
+      <c r="AE20">
+        <v>130</v>
+      </c>
+      <c r="AF20">
+        <v>179.98523890000001</v>
+      </c>
+      <c r="AG20">
+        <v>24</v>
+      </c>
+      <c r="AH20">
+        <v>11.2</v>
+      </c>
+      <c r="AI20">
+        <v>0.98128019300000002</v>
+      </c>
+      <c r="AJ20" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D21">
+        <v>99</v>
+      </c>
+      <c r="E21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21">
+        <v>317</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>317</v>
+      </c>
+      <c r="I21">
+        <v>5900</v>
+      </c>
+      <c r="J21">
+        <v>77.239999999999995</v>
+      </c>
+      <c r="K21">
+        <v>45.38</v>
+      </c>
+      <c r="L21">
+        <v>24</v>
+      </c>
+      <c r="M21">
+        <v>24</v>
+      </c>
+      <c r="N21">
+        <v>24.6</v>
+      </c>
+      <c r="O21">
+        <v>311</v>
+      </c>
+      <c r="P21">
+        <v>307</v>
+      </c>
+      <c r="Q21">
+        <v>342</v>
+      </c>
+      <c r="R21">
+        <v>308</v>
+      </c>
+      <c r="S21">
+        <v>318</v>
+      </c>
+      <c r="T21">
+        <v>340</v>
+      </c>
+      <c r="AE21">
+        <v>159</v>
+      </c>
+      <c r="AF21">
+        <v>173.7288136</v>
+      </c>
+      <c r="AG21">
+        <v>24</v>
+      </c>
+      <c r="AH21">
+        <v>13.21</v>
+      </c>
+      <c r="AI21">
+        <v>1.0105932200000001</v>
+      </c>
+      <c r="AJ21" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D22">
+        <v>99</v>
+      </c>
+      <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22">
+        <v>318</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>318</v>
+      </c>
+      <c r="I22">
+        <v>5900</v>
+      </c>
+      <c r="J22">
+        <v>77.260000000000005</v>
+      </c>
+      <c r="K22">
+        <v>45.38</v>
+      </c>
+      <c r="L22">
+        <v>24</v>
+      </c>
+      <c r="M22">
+        <v>24</v>
+      </c>
+      <c r="N22">
+        <v>25.1</v>
+      </c>
+      <c r="O22">
+        <v>314</v>
+      </c>
+      <c r="P22">
+        <v>315</v>
+      </c>
+      <c r="Q22">
+        <v>350</v>
+      </c>
+      <c r="R22">
+        <v>319</v>
+      </c>
+      <c r="S22">
+        <v>321</v>
+      </c>
+      <c r="T22">
+        <v>342</v>
+      </c>
+      <c r="AE22">
+        <v>177.3</v>
+      </c>
+      <c r="AF22">
+        <v>177.25988699999999</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>13.25</v>
+      </c>
+      <c r="AI22">
+        <v>1.1269067800000001</v>
+      </c>
+      <c r="AJ22" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D23">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23">
+        <v>320</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>320</v>
+      </c>
+      <c r="I23">
+        <v>5900</v>
+      </c>
+      <c r="J23">
+        <v>77.38</v>
+      </c>
+      <c r="K23">
+        <v>45.38</v>
+      </c>
+      <c r="L23">
+        <v>24</v>
+      </c>
+      <c r="M23">
+        <v>24</v>
+      </c>
+      <c r="N23">
+        <v>24.9</v>
+      </c>
+      <c r="O23">
+        <v>317</v>
+      </c>
+      <c r="P23">
+        <v>312</v>
+      </c>
+      <c r="Q23">
+        <v>345</v>
+      </c>
+      <c r="R23">
+        <v>315</v>
+      </c>
+      <c r="S23">
+        <v>318</v>
+      </c>
+      <c r="T23">
+        <v>339</v>
+      </c>
+      <c r="AE23">
+        <v>162</v>
+      </c>
+      <c r="AF23">
+        <v>175.84745760000001</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>13.33</v>
+      </c>
+      <c r="AI23">
+        <v>1.029661017</v>
+      </c>
+      <c r="AJ23" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D24">
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24">
+        <v>317</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>317</v>
+      </c>
+      <c r="I24">
+        <v>6150</v>
+      </c>
+      <c r="J24">
+        <v>77.66</v>
+      </c>
+      <c r="K24">
+        <v>47.31</v>
+      </c>
+      <c r="L24">
+        <v>24</v>
+      </c>
+      <c r="M24">
+        <v>24</v>
+      </c>
+      <c r="N24">
+        <v>25.4</v>
+      </c>
+      <c r="O24">
+        <v>310</v>
+      </c>
+      <c r="P24">
+        <v>305</v>
+      </c>
+      <c r="Q24">
+        <v>334</v>
+      </c>
+      <c r="R24">
+        <v>311</v>
+      </c>
+      <c r="S24">
+        <v>313</v>
+      </c>
+      <c r="T24">
+        <v>335</v>
+      </c>
+      <c r="AE24">
+        <v>164</v>
+      </c>
+      <c r="AF24">
+        <v>172.08672089999999</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>13.21</v>
+      </c>
+      <c r="AI24">
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <v>99</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25">
+        <v>310</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>310</v>
+      </c>
+      <c r="I25">
+        <v>5900</v>
+      </c>
+      <c r="J25">
+        <v>75.5</v>
+      </c>
+      <c r="K25">
+        <v>45.38</v>
+      </c>
+      <c r="L25">
+        <v>23</v>
+      </c>
+      <c r="M25">
+        <v>23</v>
+      </c>
+      <c r="N25">
+        <v>23.65</v>
+      </c>
+      <c r="O25">
+        <v>310</v>
+      </c>
+      <c r="P25">
+        <v>305</v>
+      </c>
+      <c r="Q25">
+        <v>334</v>
+      </c>
+      <c r="R25">
+        <v>311</v>
+      </c>
+      <c r="S25">
+        <v>313</v>
+      </c>
+      <c r="T25">
+        <v>335</v>
+      </c>
+      <c r="AE25">
+        <v>151</v>
+      </c>
+      <c r="AF25">
+        <v>174.2815033</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>13.48</v>
+      </c>
+      <c r="AI25">
+        <v>1.001473839</v>
+      </c>
+      <c r="AJ25" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D26">
+        <v>99</v>
+      </c>
+      <c r="E26" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26">
+        <v>320</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>320</v>
+      </c>
+      <c r="I26">
+        <v>6000</v>
+      </c>
+      <c r="J26">
+        <v>76.81</v>
+      </c>
+      <c r="K26">
+        <v>46.15</v>
+      </c>
+      <c r="L26">
+        <v>24</v>
+      </c>
+      <c r="M26">
+        <v>24</v>
+      </c>
+      <c r="N26">
+        <v>24.85</v>
+      </c>
+      <c r="O26">
+        <v>313</v>
+      </c>
+      <c r="P26">
+        <v>310</v>
+      </c>
+      <c r="Q26">
+        <v>338</v>
+      </c>
+      <c r="R26">
+        <v>311</v>
+      </c>
+      <c r="S26">
+        <v>314</v>
+      </c>
+      <c r="T26">
+        <v>332</v>
+      </c>
+      <c r="AE26">
+        <v>164</v>
+      </c>
+      <c r="AF26">
+        <v>172.56944440000001</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>13.33</v>
+      </c>
+      <c r="AI26">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="AJ26" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D27">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27">
+        <v>305</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>305</v>
+      </c>
+      <c r="I27">
+        <v>6000</v>
+      </c>
+      <c r="J27">
+        <v>76.17</v>
+      </c>
+      <c r="K27">
+        <v>46.15</v>
+      </c>
+      <c r="L27">
+        <v>23</v>
+      </c>
+      <c r="M27">
+        <v>23</v>
+      </c>
+      <c r="N27">
+        <v>23.3</v>
+      </c>
+      <c r="O27">
+        <v>308</v>
+      </c>
+      <c r="P27">
+        <v>310</v>
+      </c>
+      <c r="Q27">
+        <v>343</v>
+      </c>
+      <c r="R27">
+        <v>308</v>
+      </c>
+      <c r="S27">
+        <v>313</v>
+      </c>
+      <c r="T27">
+        <v>333</v>
+      </c>
+      <c r="AE27">
+        <v>150</v>
+      </c>
+      <c r="AF27">
+        <v>168.84057970000001</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>13.26</v>
+      </c>
+      <c r="AI27">
+        <v>0.97826086999999995</v>
+      </c>
+      <c r="AJ27" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D28">
+        <v>151</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>25</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>17.2</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>16.2</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D29">
+        <v>151</v>
+      </c>
+      <c r="E29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>9</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>16.2</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D30">
+        <v>22</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30">
+        <v>291</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>329</v>
+      </c>
+      <c r="I30">
+        <v>6201</v>
+      </c>
+      <c r="J30">
+        <v>61.4</v>
+      </c>
+      <c r="K30">
+        <v>28.9</v>
+      </c>
+      <c r="L30">
+        <v>21</v>
+      </c>
+      <c r="M30">
+        <v>21.5</v>
+      </c>
+      <c r="N30">
+        <v>25.8</v>
+      </c>
+      <c r="O30">
+        <v>310</v>
+      </c>
+      <c r="P30">
+        <v>37</v>
+      </c>
+      <c r="Q30">
+        <v>328</v>
+      </c>
+      <c r="R30">
+        <v>333</v>
+      </c>
+      <c r="S30">
+        <v>317</v>
+      </c>
+      <c r="T30">
+        <v>307</v>
+      </c>
+      <c r="U30">
+        <v>315</v>
+      </c>
+      <c r="AE30">
+        <v>210</v>
+      </c>
+      <c r="AF30">
+        <v>198.12472639999999</v>
+      </c>
+      <c r="AG30">
+        <v>21.5</v>
+      </c>
+      <c r="AH30">
+        <v>13.88</v>
+      </c>
+      <c r="AI30">
+        <v>1.45137881</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31">
+        <v>236.2</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>225.8</v>
+      </c>
+      <c r="I31">
+        <v>4680</v>
+      </c>
+      <c r="J31">
+        <v>457</v>
+      </c>
+      <c r="K31">
+        <v>60</v>
+      </c>
+      <c r="L31">
+        <v>24</v>
+      </c>
+      <c r="M31">
+        <v>24</v>
+      </c>
+      <c r="N31">
+        <v>12.1</v>
+      </c>
+      <c r="O31">
+        <v>431</v>
+      </c>
+      <c r="P31">
+        <v>489</v>
+      </c>
+      <c r="Q31">
+        <v>494</v>
+      </c>
+      <c r="R31">
+        <v>401</v>
+      </c>
+      <c r="S31">
+        <v>383</v>
+      </c>
+      <c r="T31">
+        <v>452</v>
+      </c>
+      <c r="U31">
+        <v>396</v>
+      </c>
+      <c r="V31">
+        <v>338</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>107.7279202</v>
+      </c>
+      <c r="AG31">
+        <v>24</v>
+      </c>
+      <c r="AH31">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>301</v>
+      </c>
+      <c r="E32" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32">
+        <v>236</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>264</v>
+      </c>
+      <c r="I32">
+        <v>4680</v>
+      </c>
+      <c r="J32">
+        <v>457</v>
+      </c>
+      <c r="K32">
+        <v>60</v>
+      </c>
+      <c r="L32">
+        <v>24</v>
+      </c>
+      <c r="M32">
+        <v>24</v>
+      </c>
+      <c r="N32">
+        <v>12.1</v>
+      </c>
+      <c r="O32">
+        <v>424</v>
+      </c>
+      <c r="P32">
+        <v>454</v>
+      </c>
+      <c r="Q32">
+        <v>509</v>
+      </c>
+      <c r="R32">
+        <v>401</v>
+      </c>
+      <c r="S32">
+        <v>407</v>
+      </c>
+      <c r="T32">
+        <v>467</v>
+      </c>
+      <c r="U32">
+        <v>399</v>
+      </c>
+      <c r="V32">
+        <v>365</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>107.7279202</v>
+      </c>
+      <c r="AG32">
+        <v>24</v>
+      </c>
+      <c r="AH32">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>301</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33">
+        <v>260.60000000000002</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>260.14999999999998</v>
+      </c>
+      <c r="I33">
+        <v>4680</v>
+      </c>
+      <c r="J33">
+        <v>460</v>
+      </c>
+      <c r="K33">
+        <v>60</v>
+      </c>
+      <c r="L33">
+        <v>24</v>
+      </c>
+      <c r="M33">
+        <v>24</v>
+      </c>
+      <c r="N33">
+        <v>12.5</v>
+      </c>
+      <c r="O33">
+        <v>431</v>
+      </c>
+      <c r="P33">
+        <v>489</v>
+      </c>
+      <c r="Q33">
+        <v>494</v>
+      </c>
+      <c r="R33">
+        <v>401</v>
+      </c>
+      <c r="S33">
+        <v>383</v>
+      </c>
+      <c r="T33">
+        <v>452</v>
+      </c>
+      <c r="U33">
+        <v>396</v>
+      </c>
+      <c r="V33">
+        <v>338</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>111.2891738</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>11.3</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>299</v>
+      </c>
+      <c r="E34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34">
+        <v>243.8</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>259.10000000000002</v>
+      </c>
+      <c r="I34">
+        <v>5070</v>
+      </c>
+      <c r="J34">
+        <v>459</v>
+      </c>
+      <c r="K34">
+        <v>65</v>
+      </c>
+      <c r="L34">
+        <v>24</v>
+      </c>
+      <c r="M34">
+        <v>23</v>
+      </c>
+      <c r="N34">
+        <v>11.9</v>
+      </c>
+      <c r="O34">
+        <v>431</v>
+      </c>
+      <c r="P34">
+        <v>489</v>
+      </c>
+      <c r="Q34">
+        <v>494</v>
+      </c>
+      <c r="R34">
+        <v>401</v>
+      </c>
+      <c r="S34">
+        <v>383</v>
+      </c>
+      <c r="T34">
+        <v>452</v>
+      </c>
+      <c r="U34">
+        <v>396</v>
+      </c>
+      <c r="V34">
+        <v>338</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>97.797501639999993</v>
+      </c>
+      <c r="AG34">
+        <v>24</v>
+      </c>
+      <c r="AH34">
+        <v>10.6</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="9" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46200</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>301</v>
+      </c>
+      <c r="E35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35">
+        <v>267.8</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>269.39999999999998</v>
+      </c>
+      <c r="I35">
+        <v>5070</v>
+      </c>
+      <c r="J35">
+        <v>459</v>
+      </c>
+      <c r="K35">
+        <v>65</v>
+      </c>
+      <c r="L35">
+        <v>24</v>
+      </c>
+      <c r="M35">
+        <v>24</v>
+      </c>
+      <c r="N35">
+        <v>11.5</v>
+      </c>
+      <c r="O35">
+        <v>431</v>
+      </c>
+      <c r="P35">
+        <v>489</v>
+      </c>
+      <c r="Q35">
+        <v>494</v>
+      </c>
+      <c r="R35">
+        <v>401</v>
+      </c>
+      <c r="S35">
+        <v>383</v>
+      </c>
+      <c r="T35">
+        <v>452</v>
+      </c>
+      <c r="U35">
+        <v>396</v>
+      </c>
+      <c r="V35">
+        <v>338</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>94.510190660000006</v>
+      </c>
+      <c r="AG35">
+        <v>24</v>
+      </c>
+      <c r="AH35">
+        <v>11.1</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>306</v>
+      </c>
+      <c r="E36" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36">
+        <v>316</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+      <c r="H36">
+        <v>468.7</v>
+      </c>
+      <c r="I36">
+        <v>6771</v>
+      </c>
+      <c r="J36">
+        <v>99.5</v>
+      </c>
+      <c r="K36">
+        <v>47.61</v>
+      </c>
+      <c r="L36">
+        <v>25</v>
+      </c>
+      <c r="M36">
+        <v>25</v>
+      </c>
+      <c r="N36">
+        <v>35.32</v>
+      </c>
+      <c r="O36">
+        <v>350</v>
+      </c>
+      <c r="P36">
+        <v>340</v>
+      </c>
+      <c r="Q36">
+        <v>330</v>
+      </c>
+      <c r="R36">
+        <v>320</v>
+      </c>
+      <c r="S36">
+        <v>325</v>
+      </c>
+      <c r="T36">
+        <v>340</v>
+      </c>
+      <c r="U36">
+        <v>320</v>
+      </c>
+      <c r="V36">
+        <v>325</v>
+      </c>
+      <c r="W36">
+        <v>340</v>
+      </c>
+      <c r="AE36">
+        <v>193</v>
+      </c>
+      <c r="AF36">
+        <v>208.6545562</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>12.64</v>
+      </c>
+      <c r="AI36">
+        <v>1.0261408949999999</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46195</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>306</v>
+      </c>
+      <c r="E37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37">
+        <v>307</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>447</v>
+      </c>
+      <c r="I37">
+        <v>6046</v>
+      </c>
+      <c r="J37">
+        <v>98.85</v>
+      </c>
+      <c r="K37">
+        <v>42.52</v>
+      </c>
+      <c r="L37">
+        <v>24</v>
+      </c>
+      <c r="M37">
+        <v>24</v>
+      </c>
+      <c r="N37">
+        <v>32.14</v>
+      </c>
+      <c r="O37">
+        <v>345</v>
+      </c>
+      <c r="P37">
+        <v>340</v>
+      </c>
+      <c r="Q37">
+        <v>320</v>
+      </c>
+      <c r="R37">
+        <v>320</v>
+      </c>
+      <c r="S37">
+        <v>320</v>
+      </c>
+      <c r="T37">
+        <v>340</v>
+      </c>
+      <c r="U37">
+        <v>330</v>
+      </c>
+      <c r="V37">
+        <v>325</v>
+      </c>
+      <c r="W37">
+        <v>340</v>
+      </c>
+      <c r="AE37">
+        <v>173</v>
+      </c>
+      <c r="AF37">
+        <v>221.4963061</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>12.79</v>
+      </c>
+      <c r="AI37">
+        <v>1.0730234869999999</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46196</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+      <c r="D38" t="s">
+        <v>309</v>
+      </c>
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38">
+        <v>372</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>465.3</v>
+      </c>
+      <c r="I38">
+        <v>6478</v>
+      </c>
+      <c r="J38">
+        <v>102.9</v>
+      </c>
+      <c r="K38">
+        <v>45.55</v>
+      </c>
+      <c r="L38">
+        <v>24</v>
+      </c>
+      <c r="M38">
+        <v>24</v>
+      </c>
+      <c r="N38">
+        <v>33.18</v>
+      </c>
+      <c r="O38">
+        <v>355</v>
+      </c>
+      <c r="P38">
+        <v>350</v>
+      </c>
+      <c r="Q38">
+        <v>330</v>
+      </c>
+      <c r="R38">
+        <v>330</v>
+      </c>
+      <c r="S38">
+        <v>330</v>
+      </c>
+      <c r="T38">
+        <v>350</v>
+      </c>
+      <c r="U38">
+        <v>330</v>
+      </c>
+      <c r="V38">
+        <v>330</v>
+      </c>
+      <c r="W38">
+        <v>345</v>
+      </c>
+      <c r="AE38">
+        <v>180</v>
+      </c>
+      <c r="AF38">
+        <v>213.4146341</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>15.5</v>
+      </c>
+      <c r="AI38">
+        <v>1.0419882680000001</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0</v>
+      </c>
+      <c r="D39" t="s">
+        <v>306</v>
+      </c>
+      <c r="E39" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39">
+        <v>404</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+      <c r="H39">
+        <v>490</v>
+      </c>
+      <c r="I39">
+        <v>6954</v>
+      </c>
+      <c r="J39">
+        <v>104</v>
+      </c>
+      <c r="K39">
+        <v>46</v>
+      </c>
+      <c r="L39">
+        <v>25</v>
+      </c>
+      <c r="M39">
+        <v>25</v>
+      </c>
+      <c r="N39">
+        <v>34.6</v>
+      </c>
+      <c r="O39">
+        <v>360</v>
+      </c>
+      <c r="P39">
+        <v>350</v>
+      </c>
+      <c r="Q39">
+        <v>340</v>
+      </c>
+      <c r="R39">
+        <v>330</v>
+      </c>
+      <c r="S39">
+        <v>325</v>
+      </c>
+      <c r="T39">
+        <v>360</v>
+      </c>
+      <c r="U39">
+        <v>335</v>
+      </c>
+      <c r="V39">
+        <v>330</v>
+      </c>
+      <c r="W39">
+        <v>345</v>
+      </c>
+      <c r="AE39">
+        <v>190</v>
+      </c>
+      <c r="AF39">
+        <v>199.02214549999999</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>16.16</v>
+      </c>
+      <c r="AI39">
+        <v>0.98360655699999999</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46199</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0</v>
+      </c>
+      <c r="D40" t="s">
+        <v>306</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>5.9</v>
+      </c>
+      <c r="M40">
+        <v>24</v>
+      </c>
+      <c r="N40">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AE40">
+        <v>33</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>1.65</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>9.166666666666666E-2</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46197</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.15833333333333333</v>
+      </c>
+      <c r="D41" t="s">
+        <v>313</v>
+      </c>
+      <c r="E41" t="s">
+        <v>139</v>
+      </c>
+      <c r="F41">
+        <v>13</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>13</v>
+      </c>
+      <c r="I41">
+        <v>2582.9</v>
+      </c>
+      <c r="J41">
+        <v>66.3</v>
+      </c>
+      <c r="K41">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="L41">
+        <v>1.4</v>
+      </c>
+      <c r="M41">
+        <v>1.6</v>
+      </c>
+      <c r="N41">
+        <v>0.6</v>
+      </c>
+      <c r="AE41">
+        <v>8</v>
+      </c>
+      <c r="AF41">
+        <v>165.9264503</v>
+      </c>
+      <c r="AG41">
+        <v>1.6</v>
+      </c>
+      <c r="AH41">
+        <v>8.5</v>
+      </c>
+      <c r="AI41">
+        <v>1.9911174039999999</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46198</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>313</v>
+      </c>
+      <c r="E42" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42">
+        <v>345</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>339</v>
+      </c>
+      <c r="I42">
+        <v>6109.3</v>
+      </c>
+      <c r="J42">
+        <v>102.8</v>
+      </c>
+      <c r="K42">
+        <v>42.9</v>
+      </c>
+      <c r="L42">
+        <v>21.6</v>
+      </c>
+      <c r="M42">
+        <v>21.6</v>
+      </c>
+      <c r="N42">
+        <v>25.2</v>
+      </c>
+      <c r="O42">
+        <v>352</v>
+      </c>
+      <c r="P42">
+        <v>360</v>
+      </c>
+      <c r="Q42">
+        <v>361</v>
+      </c>
+      <c r="R42">
+        <v>363</v>
+      </c>
+      <c r="S42">
+        <v>354</v>
+      </c>
+      <c r="T42">
+        <v>368</v>
+      </c>
+      <c r="U42">
+        <v>353</v>
+      </c>
+      <c r="V42">
+        <v>364</v>
+      </c>
+      <c r="W42">
+        <v>368</v>
+      </c>
+      <c r="AE42">
+        <v>143</v>
+      </c>
+      <c r="AF42">
+        <v>190.96568619999999</v>
+      </c>
+      <c r="AG42">
+        <v>6</v>
+      </c>
+      <c r="AH42">
+        <v>15.97</v>
+      </c>
+      <c r="AI42">
+        <v>0.97528904000000005</v>
+      </c>
+      <c r="AJ42" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC02271-412F-4019-8A2C-3CDDF933B004}">
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
